--- a/access_control_forms/018_virtual_desktop_access_license_request_form--access_control_forms.xlsx
+++ b/access_control_forms/018_virtual_desktop_access_license_request_form--access_control_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>submitter_department</t>
+          <t>Submitter Department</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>submitter_job_title</t>
+          <t>Submitter Job Title</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>submitter_location</t>
+          <t>Submitter Location</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,40 +607,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>submitter_date</t>
+          <t>approver</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>submitter_date</t>
+          <t>Approver</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>approver_department</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Approver</t>
+          <t>Approver Department</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>approver_department</t>
+          <t>approver_location</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>approver_department</t>
+          <t>Approver Location</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>approver_location</t>
+          <t>submitter_note</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>approver_location</t>
+          <t>Submitter Note</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>submitter_note</t>
+          <t>approver_note</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Submitter Note</t>
+          <t>Approver Note</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,40 +722,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>approver_note</t>
+          <t>approval_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Approver Note</t>
+          <t>Approval Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>approval_date</t>
+          <t>submitter_email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>approval_date</t>
+          <t>Submitter Email</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>submitter_phone</t>
+          <t>approver_email</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>submitter_phone</t>
+          <t>Approver Email</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>approver_email</t>
+          <t>supporting_document1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Approver Email</t>
+          <t>Supporting Document 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submitter_email</t>
+          <t>supporting_document2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>submitter_email</t>
+          <t>Supporting Document 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>supporting_document</t>
+          <t>approver_phone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>supporting_document</t>
+          <t>Approver Phone</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>supporting_document2</t>
+          <t>submitter_job_title_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>supporting_document2</t>
+          <t>Submitter Job Title 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>approver_phone</t>
+          <t>approver_job_title</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Approver Phone</t>
+          <t>Approver Job Title</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>submitter_job_title</t>
+          <t>approver_comment</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>submitter_job_title</t>
+          <t>Approver Comment</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>submitter_department</t>
+          <t>submitter_phone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>submitter_department</t>
+          <t>Submitter Phone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,136 +952,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>submitter_location</t>
+          <t>supporting_document3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>submitter_location</t>
+          <t>Supporting Document 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>approver_job_title</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>approver_job_title</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>approver_department</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>approver_department</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>approver_location</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>approver_location</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>supporting_document3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>supporting_document3</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>approver_comment</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Approver Comment</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'IT'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'On-site'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1152,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>submitter_location_choices</t>
+          <t>approver_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'hybrid'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Hybrid'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'it'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'IT'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'manager'}</t>
+          <t>director</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Manager'}</t>
+          <t>Director</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1220,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'director'}</t>
+          <t>cto</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Director'}</t>
+          <t>CTO</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>approver_choices</t>
+          <t>approver_department_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'cto'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'CTO'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'it'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'IT'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'engineering'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Engineering'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'finance'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Finance'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'sales'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Sales'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1322,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'marketing'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Marketing'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>approver_department_choices</t>
+          <t>approver_location_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'remote'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Remote'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1488,335 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'on-site'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'On-site'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>approver_location_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'value': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>submitter_department_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'value':_'it'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'value': 'IT'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>submitter_department_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'value':_'engineering'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'value': 'Engineering'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>submitter_department_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'value':_'finance'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'value': 'Finance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>submitter_department_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'value':_'sales'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'value': 'Sales'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>submitter_department_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'value':_'marketing'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'value': 'Marketing'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>submitter_department_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'value': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>submitter_location_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'value':_'remote'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'value': 'Remote'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>submitter_location_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'value':_'on-site'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'value': 'On-site'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>submitter_location_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'value':_'hybrid'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'value': 'Hybrid'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>approver_department_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'value':_'it'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'value': 'IT'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>approver_department_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'value':_'engineering'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'value': 'Engineering'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>approver_department_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'value':_'finance'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'value': 'Finance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>approver_department_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'value':_'sales'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'value': 'Sales'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>approver_department_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'value':_'marketing'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'value': 'Marketing'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>approver_department_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'value': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>approver_location_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'value':_'remote'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'value': 'Remote'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>approver_location_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'value':_'on-site'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'value': 'On-site'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>approver_location_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'value':_'hybrid'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'value': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
